--- a/docs/PPG/Discentes.xlsx
+++ b/docs/PPG/Discentes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5FCEA5C-EC91-FB45-B2A8-8EE1D9B48B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CB8046B-951D-464C-BAD4-101291FE8BEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="840" yWindow="660" windowWidth="29380" windowHeight="18940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="880" yWindow="660" windowWidth="29360" windowHeight="18940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Discentes" sheetId="9" r:id="rId1"/>
@@ -2390,37 +2390,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{0B994284-E167-D14C-9C75-CB66973B77E8}"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2458,9 +2428,9 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="stats3-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="6"/>
-      <tableStyleElement type="firstRowStripe" dxfId="5"/>
-      <tableStyleElement type="secondRowStripe" dxfId="4"/>
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -14692,9 +14662,11 @@
         <v>666</v>
       </c>
       <c r="D544" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E544" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="E544" s="6">
+        <v>46092</v>
+      </c>
       <c r="F544" s="10" t="s">
         <v>13</v>
       </c>
@@ -19258,7 +19230,7 @@
     <sortCondition ref="B2:B557"/>
   </sortState>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="3" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/docs/PPG/Discentes.xlsx
+++ b/docs/PPG/Discentes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CB8046B-951D-464C-BAD4-101291FE8BEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECC94159-2E41-8E4A-A11D-3DF9464BA292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="660" windowWidth="29360" windowHeight="18940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13434,9 +13434,11 @@
         <v>44788</v>
       </c>
       <c r="D486" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E486" s="6"/>
+        <v>5</v>
+      </c>
+      <c r="E486" s="6">
+        <v>45565</v>
+      </c>
       <c r="F486" s="10" t="s">
         <v>13</v>
       </c>
@@ -15951,9 +15953,11 @@
         <v>687</v>
       </c>
       <c r="D605" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E605" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="E605" s="6">
+        <v>46099</v>
+      </c>
       <c r="F605" s="10" t="s">
         <v>13</v>
       </c>
@@ -16138,9 +16142,11 @@
         <v>690</v>
       </c>
       <c r="D614" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E614" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="E614" s="6">
+        <v>46157</v>
+      </c>
       <c r="F614" s="10" t="s">
         <v>328</v>
       </c>

--- a/docs/PPG/Discentes.xlsx
+++ b/docs/PPG/Discentes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECC94159-2E41-8E4A-A11D-3DF9464BA292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6401A2E-9BF3-E643-87CC-45B6E39E5AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="660" windowWidth="29360" windowHeight="18940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14429,9 +14429,11 @@
         <v>660</v>
       </c>
       <c r="D533" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E533" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="E533" s="6">
+        <v>46105</v>
+      </c>
       <c r="F533" s="10" t="s">
         <v>13</v>
       </c>
@@ -14838,9 +14840,11 @@
         <v>45161</v>
       </c>
       <c r="D552" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E552" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="E552" s="6">
+        <v>46105</v>
+      </c>
       <c r="F552" s="10" t="s">
         <v>13</v>
       </c>

--- a/docs/PPG/Discentes.xlsx
+++ b/docs/PPG/Discentes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6401A2E-9BF3-E643-87CC-45B6E39E5AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70823FD2-6BCF-AC44-AE14-C595C360773F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="660" windowWidth="29360" windowHeight="18940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14034,7 +14034,7 @@
         <v>649</v>
       </c>
       <c r="D514" s="5" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E514" s="6"/>
       <c r="F514" s="10" t="s">
@@ -14357,7 +14357,7 @@
         <v>658</v>
       </c>
       <c r="D529" s="5" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E529" s="6"/>
       <c r="F529" s="10"/>
@@ -14395,7 +14395,7 @@
         <v>658</v>
       </c>
       <c r="D531" s="5" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E531" s="6"/>
       <c r="F531" s="10"/>
@@ -14580,7 +14580,7 @@
         <v>664</v>
       </c>
       <c r="D540" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E540" s="6"/>
       <c r="F540" s="10" t="s">
@@ -14624,7 +14624,7 @@
         <v>45117</v>
       </c>
       <c r="D542" s="5" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E542" s="6"/>
       <c r="F542" s="10" t="s">
@@ -14689,7 +14689,7 @@
         <v>45133</v>
       </c>
       <c r="D545" s="5" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E545" s="6"/>
       <c r="F545" s="10" t="s">
@@ -14773,7 +14773,7 @@
         <v>45146</v>
       </c>
       <c r="D549" s="5" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E549" s="6"/>
       <c r="F549" s="10" t="s">
@@ -14993,9 +14993,11 @@
         <v>669</v>
       </c>
       <c r="D559" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E559" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="E559" s="6">
+        <v>46083</v>
+      </c>
       <c r="F559" s="10" t="s">
         <v>13</v>
       </c>
@@ -15037,7 +15039,7 @@
         <v>669</v>
       </c>
       <c r="D561" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E561" s="6"/>
       <c r="F561" s="10" t="s">
@@ -15058,7 +15060,7 @@
         <v>45282</v>
       </c>
       <c r="D562" s="5" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E562" s="6"/>
       <c r="F562" s="10" t="s">
@@ -15795,7 +15797,7 @@
         <v>681</v>
       </c>
       <c r="D597" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E597" s="6"/>
       <c r="F597" s="10"/>
@@ -15812,7 +15814,7 @@
         <v>682</v>
       </c>
       <c r="D598" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E598" s="6"/>
       <c r="F598" s="10"/>
@@ -16686,9 +16688,11 @@
         <v>45701</v>
       </c>
       <c r="D640" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E640" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="E640" s="6">
+        <v>46164</v>
+      </c>
       <c r="F640" s="10" t="s">
         <v>13</v>
       </c>

--- a/docs/PPG/Discentes.xlsx
+++ b/docs/PPG/Discentes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70823FD2-6BCF-AC44-AE14-C595C360773F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D8F640-889C-5442-AE91-2FC88812D788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="660" windowWidth="29360" windowHeight="18940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Discentes" sheetId="9" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Discentes!$A$1:$G$655</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Discentes!$A$1:$G$654</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3492" uniqueCount="734">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3597" uniqueCount="769">
   <si>
     <t>Pré-inscrito</t>
   </si>
@@ -2241,6 +2241,111 @@
   </si>
   <si>
     <t>12/02/2026</t>
+  </si>
+  <si>
+    <t>Alessandra da Silva</t>
+  </si>
+  <si>
+    <t>Carla de Freitas Ribeiro</t>
+  </si>
+  <si>
+    <t>Cinthya Beatriz Martins Alves</t>
+  </si>
+  <si>
+    <t>Lucas Pires Machado Caxias</t>
+  </si>
+  <si>
+    <t>Veronica Cristina Vieira Barbosa</t>
+  </si>
+  <si>
+    <t>Fernanda Maria do Nascimento</t>
+  </si>
+  <si>
+    <t>Fernanda Santa Rita Marques</t>
+  </si>
+  <si>
+    <t>Lidiane Priscila Costa Cavalcante</t>
+  </si>
+  <si>
+    <t>Rafael Valle</t>
+  </si>
+  <si>
+    <t>Silvania Cristina Gualberto Lopes</t>
+  </si>
+  <si>
+    <t>Stephanie Raposo Gomes</t>
+  </si>
+  <si>
+    <t>Ingrid Pantarotti Dantas</t>
+  </si>
+  <si>
+    <t>Rony Wellington Corrêa Pessoa</t>
+  </si>
+  <si>
+    <t>Thalita Moreira de Rezende</t>
+  </si>
+  <si>
+    <t>Mariana Reginaldo da Silva</t>
+  </si>
+  <si>
+    <t>Barbara Moreira Canabrava</t>
+  </si>
+  <si>
+    <t>Natália Sardinha Marques</t>
+  </si>
+  <si>
+    <t>Luã Domingos Pompilio da Silva</t>
+  </si>
+  <si>
+    <t>Nanci dos Santos Montenegro</t>
+  </si>
+  <si>
+    <t>Gilmara dos Santos Bento</t>
+  </si>
+  <si>
+    <t>Anita Maria Alcalá Pages</t>
+  </si>
+  <si>
+    <t>Eduardo Carpinelli dos Santos</t>
+  </si>
+  <si>
+    <t>Isabela Garcia Pedrosa da Cruz Vieira</t>
+  </si>
+  <si>
+    <t>Jobson de Sousa Targino</t>
+  </si>
+  <si>
+    <t>Kamylla Martins</t>
+  </si>
+  <si>
+    <t>Leandro Rabelo Fraga</t>
+  </si>
+  <si>
+    <t>Tamires da Silva Bittencourt</t>
+  </si>
+  <si>
+    <t>Arthur Rios Gomes</t>
+  </si>
+  <si>
+    <t>Luis Alberto Figueiredo Menezes</t>
+  </si>
+  <si>
+    <t>Fernanda de Andrade Nogueira</t>
+  </si>
+  <si>
+    <t>João Emilio Rezende de Carvalho</t>
+  </si>
+  <si>
+    <t>Joyce Figueira dos Prazeres</t>
+  </si>
+  <si>
+    <t>Thiago Bomfim Campos Dantas</t>
+  </si>
+  <si>
+    <t>Maria Elisabete Cartolano</t>
+  </si>
+  <si>
+    <t>Thamires Goncalves Pinto</t>
   </si>
 </sst>
 </file>
@@ -2390,7 +2495,17 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{0B994284-E167-D14C-9C75-CB66973B77E8}"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2428,9 +2543,9 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="stats3-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="headerRow" dxfId="4"/>
+      <tableStyleElement type="firstRowStripe" dxfId="3"/>
+      <tableStyleElement type="secondRowStripe" dxfId="2"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2642,7 +2757,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:G919"/>
+  <dimension ref="A1:G917"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43.33203125" style="4" customWidth="1"/>
@@ -15161,13 +15276,15 @@
       <c r="B567" s="5" t="s">
         <v>545</v>
       </c>
-      <c r="C567" s="6">
-        <v>45287</v>
+      <c r="C567" s="6" t="s">
+        <v>671</v>
       </c>
       <c r="D567" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E567" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="E567" s="6">
+        <v>46128</v>
+      </c>
       <c r="F567" s="10" t="s">
         <v>13</v>
       </c>
@@ -15180,15 +15297,17 @@
         <v>11</v>
       </c>
       <c r="B568" s="5" t="s">
-        <v>545</v>
-      </c>
-      <c r="C568" s="6" t="s">
-        <v>671</v>
+        <v>546</v>
+      </c>
+      <c r="C568" s="6">
+        <v>45287</v>
       </c>
       <c r="D568" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E568" s="6"/>
+        <v>5</v>
+      </c>
+      <c r="E568" s="6">
+        <v>45992</v>
+      </c>
       <c r="F568" s="10" t="s">
         <v>13</v>
       </c>
@@ -15201,17 +15320,15 @@
         <v>11</v>
       </c>
       <c r="B569" s="5" t="s">
-        <v>546</v>
-      </c>
-      <c r="C569" s="6">
-        <v>45287</v>
+        <v>549</v>
+      </c>
+      <c r="C569" s="6" t="s">
+        <v>671</v>
       </c>
       <c r="D569" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E569" s="6">
-        <v>45992</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E569" s="6"/>
       <c r="F569" s="10" t="s">
         <v>13</v>
       </c>
@@ -15224,17 +15341,17 @@
         <v>11</v>
       </c>
       <c r="B570" s="5" t="s">
-        <v>549</v>
-      </c>
-      <c r="C570" s="6" t="s">
-        <v>671</v>
+        <v>548</v>
+      </c>
+      <c r="C570" s="6">
+        <v>45287</v>
       </c>
       <c r="D570" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E570" s="6"/>
       <c r="F570" s="10" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="G570" s="10" t="s">
         <v>14</v>
@@ -15245,17 +15362,17 @@
         <v>11</v>
       </c>
       <c r="B571" s="5" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C571" s="6">
         <v>45287</v>
       </c>
       <c r="D571" s="5" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E571" s="6"/>
       <c r="F571" s="10" t="s">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="G571" s="10" t="s">
         <v>14</v>
@@ -15263,16 +15380,16 @@
     </row>
     <row r="572" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A572" s="5" t="s">
-        <v>11</v>
+        <v>166</v>
       </c>
       <c r="B572" s="5" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="C572" s="6">
-        <v>45287</v>
+        <v>45293</v>
       </c>
       <c r="D572" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E572" s="6"/>
       <c r="F572" s="10" t="s">
@@ -15287,13 +15404,13 @@
         <v>166</v>
       </c>
       <c r="B573" s="5" t="s">
-        <v>551</v>
-      </c>
-      <c r="C573" s="6">
-        <v>45293</v>
+        <v>550</v>
+      </c>
+      <c r="C573" s="6" t="s">
+        <v>672</v>
       </c>
       <c r="D573" s="5" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E573" s="6"/>
       <c r="F573" s="10" t="s">
@@ -15305,16 +15422,16 @@
     </row>
     <row r="574" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A574" s="5" t="s">
-        <v>166</v>
+        <v>11</v>
       </c>
       <c r="B574" s="5" t="s">
-        <v>550</v>
-      </c>
-      <c r="C574" s="6" t="s">
-        <v>672</v>
+        <v>553</v>
+      </c>
+      <c r="C574" s="6">
+        <v>45294</v>
       </c>
       <c r="D574" s="5" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E574" s="6"/>
       <c r="F574" s="10" t="s">
@@ -15329,17 +15446,19 @@
         <v>11</v>
       </c>
       <c r="B575" s="5" t="s">
-        <v>553</v>
-      </c>
-      <c r="C575" s="6">
-        <v>45294</v>
+        <v>552</v>
+      </c>
+      <c r="C575" s="6" t="s">
+        <v>673</v>
       </c>
       <c r="D575" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E575" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="E575" s="6">
+        <v>46013</v>
+      </c>
       <c r="F575" s="10" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="G575" s="10" t="s">
         <v>14</v>
@@ -15347,22 +15466,20 @@
     </row>
     <row r="576" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A576" s="5" t="s">
-        <v>11</v>
+        <v>166</v>
       </c>
       <c r="B576" s="5" t="s">
-        <v>552</v>
-      </c>
-      <c r="C576" s="6" t="s">
-        <v>673</v>
+        <v>397</v>
+      </c>
+      <c r="C576" s="6">
+        <v>45294</v>
       </c>
       <c r="D576" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E576" s="6">
-        <v>46013</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E576" s="6"/>
       <c r="F576" s="10" t="s">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="G576" s="10" t="s">
         <v>14</v>
@@ -15373,17 +15490,17 @@
         <v>166</v>
       </c>
       <c r="B577" s="5" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="C577" s="6">
         <v>45294</v>
       </c>
       <c r="D577" s="5" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E577" s="6"/>
       <c r="F577" s="10" t="s">
-        <v>13</v>
+        <v>359</v>
       </c>
       <c r="G577" s="10" t="s">
         <v>14</v>
@@ -15394,17 +15511,17 @@
         <v>166</v>
       </c>
       <c r="B578" s="5" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="C578" s="6">
-        <v>45294</v>
+        <v>45295</v>
       </c>
       <c r="D578" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E578" s="6"/>
       <c r="F578" s="10" t="s">
-        <v>359</v>
+        <v>13</v>
       </c>
       <c r="G578" s="10" t="s">
         <v>14</v>
@@ -15415,7 +15532,7 @@
         <v>166</v>
       </c>
       <c r="B579" s="5" t="s">
-        <v>391</v>
+        <v>443</v>
       </c>
       <c r="C579" s="6">
         <v>45295</v>
@@ -15433,21 +15550,21 @@
     </row>
     <row r="580" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A580" s="5" t="s">
-        <v>166</v>
+        <v>11</v>
       </c>
       <c r="B580" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="C580" s="6">
-        <v>45295</v>
+        <v>554</v>
+      </c>
+      <c r="C580" s="6" t="s">
+        <v>674</v>
       </c>
       <c r="D580" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E580" s="6"/>
-      <c r="F580" s="10" t="s">
-        <v>13</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E580" s="6">
+        <v>46155</v>
+      </c>
+      <c r="F580" s="10"/>
       <c r="G580" s="10" t="s">
         <v>14</v>
       </c>
@@ -15457,27 +15574,31 @@
         <v>11</v>
       </c>
       <c r="B581" s="5" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C581" s="6" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D581" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E581" s="6"/>
-      <c r="F581" s="10"/>
-      <c r="G581" s="10"/>
+      <c r="F581" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G581" s="10" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="582" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A582" s="5" t="s">
-        <v>11</v>
+        <v>166</v>
       </c>
       <c r="B582" s="5" t="s">
-        <v>555</v>
+        <v>340</v>
       </c>
       <c r="C582" s="6" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D582" s="5" t="s">
         <v>1</v>
@@ -15492,20 +15613,20 @@
     </row>
     <row r="583" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A583" s="5" t="s">
-        <v>166</v>
+        <v>11</v>
       </c>
       <c r="B583" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="C583" s="6" t="s">
-        <v>676</v>
+        <v>607</v>
+      </c>
+      <c r="C583" s="6">
+        <v>45344</v>
       </c>
       <c r="D583" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E583" s="6"/>
       <c r="F583" s="10" t="s">
-        <v>13</v>
+        <v>300</v>
       </c>
       <c r="G583" s="10" t="s">
         <v>14</v>
@@ -15516,10 +15637,10 @@
         <v>11</v>
       </c>
       <c r="B584" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="C584" s="6">
-        <v>45344</v>
+        <v>636</v>
+      </c>
+      <c r="C584" s="6" t="s">
+        <v>677</v>
       </c>
       <c r="D584" s="5" t="s">
         <v>1</v>
@@ -15537,7 +15658,7 @@
         <v>11</v>
       </c>
       <c r="B585" s="5" t="s">
-        <v>636</v>
+        <v>556</v>
       </c>
       <c r="C585" s="6" t="s">
         <v>677</v>
@@ -15547,7 +15668,7 @@
       </c>
       <c r="E585" s="6"/>
       <c r="F585" s="10" t="s">
-        <v>300</v>
+        <v>13</v>
       </c>
       <c r="G585" s="10" t="s">
         <v>14</v>
@@ -15558,15 +15679,17 @@
         <v>11</v>
       </c>
       <c r="B586" s="5" t="s">
-        <v>556</v>
+        <v>509</v>
       </c>
       <c r="C586" s="6" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D586" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E586" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="E586" s="6">
+        <v>46007</v>
+      </c>
       <c r="F586" s="10" t="s">
         <v>13</v>
       </c>
@@ -15579,16 +15702,16 @@
         <v>11</v>
       </c>
       <c r="B587" s="5" t="s">
-        <v>509</v>
-      </c>
-      <c r="C587" s="6" t="s">
-        <v>678</v>
+        <v>558</v>
+      </c>
+      <c r="C587" s="6">
+        <v>45348</v>
       </c>
       <c r="D587" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E587" s="6">
-        <v>46007</v>
+        <v>45786</v>
       </c>
       <c r="F587" s="10" t="s">
         <v>13</v>
@@ -15602,17 +15725,15 @@
         <v>11</v>
       </c>
       <c r="B588" s="5" t="s">
-        <v>558</v>
-      </c>
-      <c r="C588" s="6">
-        <v>45348</v>
+        <v>559</v>
+      </c>
+      <c r="C588" s="6" t="s">
+        <v>679</v>
       </c>
       <c r="D588" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E588" s="6">
-        <v>45786</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E588" s="6"/>
       <c r="F588" s="10" t="s">
         <v>13</v>
       </c>
@@ -15622,20 +15743,20 @@
     </row>
     <row r="589" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A589" s="5" t="s">
-        <v>11</v>
+        <v>166</v>
       </c>
       <c r="B589" s="5" t="s">
-        <v>559</v>
-      </c>
-      <c r="C589" s="6" t="s">
-        <v>679</v>
+        <v>561</v>
+      </c>
+      <c r="C589" s="6">
+        <v>45351</v>
       </c>
       <c r="D589" s="5" t="s">
-        <v>1</v>
+        <v>435</v>
       </c>
       <c r="E589" s="6"/>
       <c r="F589" s="10" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G589" s="10" t="s">
         <v>14</v>
@@ -15648,11 +15769,11 @@
       <c r="B590" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="C590" s="6">
-        <v>45351</v>
+      <c r="C590" s="6" t="s">
+        <v>680</v>
       </c>
       <c r="D590" s="5" t="s">
-        <v>435</v>
+        <v>1</v>
       </c>
       <c r="E590" s="6"/>
       <c r="F590" s="10" t="s">
@@ -15667,7 +15788,7 @@
         <v>166</v>
       </c>
       <c r="B591" s="5" t="s">
-        <v>561</v>
+        <v>446</v>
       </c>
       <c r="C591" s="6" t="s">
         <v>680</v>
@@ -15677,7 +15798,7 @@
       </c>
       <c r="E591" s="6"/>
       <c r="F591" s="10" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="G591" s="10" t="s">
         <v>14</v>
@@ -15688,7 +15809,7 @@
         <v>166</v>
       </c>
       <c r="B592" s="5" t="s">
-        <v>446</v>
+        <v>560</v>
       </c>
       <c r="C592" s="6" t="s">
         <v>680</v>
@@ -15706,60 +15827,60 @@
     </row>
     <row r="593" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A593" s="5" t="s">
-        <v>166</v>
+        <v>11</v>
       </c>
       <c r="B593" s="5" t="s">
-        <v>560</v>
-      </c>
-      <c r="C593" s="6" t="s">
-        <v>680</v>
+        <v>562</v>
+      </c>
+      <c r="C593" s="6">
+        <v>45351</v>
       </c>
       <c r="D593" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E593" s="6"/>
-      <c r="F593" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G593" s="10" t="s">
-        <v>14</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E593" s="6">
+        <v>46059</v>
+      </c>
+      <c r="F593" s="10"/>
+      <c r="G593" s="10"/>
     </row>
     <row r="594" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A594" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B594" s="5" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C594" s="6">
-        <v>45351</v>
+        <v>45356</v>
       </c>
       <c r="D594" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E594" s="6">
-        <v>46059</v>
-      </c>
-      <c r="F594" s="10"/>
-      <c r="G594" s="10"/>
+        <v>1</v>
+      </c>
+      <c r="E594" s="6"/>
+      <c r="F594" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="G594" s="10" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="595" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A595" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B595" s="5" t="s">
-        <v>563</v>
+        <v>608</v>
       </c>
       <c r="C595" s="6">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D595" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E595" s="6"/>
       <c r="F595" s="10" t="s">
-        <v>219</v>
+        <v>300</v>
       </c>
       <c r="G595" s="10" t="s">
         <v>14</v>
@@ -15770,31 +15891,27 @@
         <v>11</v>
       </c>
       <c r="B596" s="5" t="s">
-        <v>608</v>
-      </c>
-      <c r="C596" s="6">
-        <v>45357</v>
+        <v>564</v>
+      </c>
+      <c r="C596" s="6" t="s">
+        <v>681</v>
       </c>
       <c r="D596" s="5" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E596" s="6"/>
-      <c r="F596" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="G596" s="10" t="s">
-        <v>14</v>
-      </c>
+      <c r="F596" s="10"/>
+      <c r="G596" s="10"/>
     </row>
     <row r="597" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A597" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B597" s="5" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C597" s="6" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D597" s="5" t="s">
         <v>5</v>
@@ -15808,32 +15925,38 @@
         <v>11</v>
       </c>
       <c r="B598" s="5" t="s">
-        <v>565</v>
+        <v>163</v>
       </c>
       <c r="C598" s="6" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D598" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E598" s="6"/>
-      <c r="F598" s="10"/>
-      <c r="G598" s="10"/>
+      <c r="F598" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G598" s="10" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="599" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A599" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B599" s="5" t="s">
-        <v>163</v>
+        <v>568</v>
       </c>
       <c r="C599" s="6" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D599" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E599" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="E599" s="6">
+        <v>46155</v>
+      </c>
       <c r="F599" s="10" t="s">
         <v>13</v>
       </c>
@@ -15846,7 +15969,7 @@
         <v>11</v>
       </c>
       <c r="B600" s="5" t="s">
-        <v>568</v>
+        <v>163</v>
       </c>
       <c r="C600" s="6" t="s">
         <v>684</v>
@@ -15867,15 +15990,17 @@
         <v>11</v>
       </c>
       <c r="B601" s="5" t="s">
-        <v>163</v>
+        <v>557</v>
       </c>
       <c r="C601" s="6" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D601" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E601" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="E601" s="6">
+        <v>46098</v>
+      </c>
       <c r="F601" s="10" t="s">
         <v>13</v>
       </c>
@@ -15888,13 +16013,13 @@
         <v>11</v>
       </c>
       <c r="B602" s="5" t="s">
-        <v>557</v>
+        <v>609</v>
       </c>
       <c r="C602" s="6" t="s">
         <v>685</v>
       </c>
       <c r="D602" s="5" t="s">
-        <v>435</v>
+        <v>4</v>
       </c>
       <c r="E602" s="6"/>
       <c r="F602" s="10" t="s">
@@ -15909,17 +16034,19 @@
         <v>11</v>
       </c>
       <c r="B603" s="5" t="s">
-        <v>609</v>
+        <v>567</v>
       </c>
       <c r="C603" s="6" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D603" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E603" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="E603" s="6">
+        <v>45954</v>
+      </c>
       <c r="F603" s="10" t="s">
-        <v>13</v>
+        <v>300</v>
       </c>
       <c r="G603" s="10" t="s">
         <v>14</v>
@@ -15930,19 +16057,19 @@
         <v>11</v>
       </c>
       <c r="B604" s="5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C604" s="6" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D604" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E604" s="6">
-        <v>45954</v>
+        <v>46099</v>
       </c>
       <c r="F604" s="10" t="s">
-        <v>300</v>
+        <v>13</v>
       </c>
       <c r="G604" s="10" t="s">
         <v>14</v>
@@ -15953,17 +16080,15 @@
         <v>11</v>
       </c>
       <c r="B605" s="5" t="s">
-        <v>566</v>
+        <v>468</v>
       </c>
       <c r="C605" s="6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D605" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E605" s="6">
-        <v>46099</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E605" s="6"/>
       <c r="F605" s="10" t="s">
         <v>13</v>
       </c>
@@ -15976,17 +16101,17 @@
         <v>11</v>
       </c>
       <c r="B606" s="5" t="s">
-        <v>468</v>
+        <v>569</v>
       </c>
       <c r="C606" s="6" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D606" s="5" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E606" s="6"/>
       <c r="F606" s="10" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="G606" s="10" t="s">
         <v>14</v>
@@ -15997,7 +16122,7 @@
         <v>11</v>
       </c>
       <c r="B607" s="5" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C607" s="6" t="s">
         <v>689</v>
@@ -16007,7 +16132,7 @@
       </c>
       <c r="E607" s="6"/>
       <c r="F607" s="10" t="s">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="G607" s="10" t="s">
         <v>14</v>
@@ -16015,10 +16140,10 @@
     </row>
     <row r="608" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A608" s="5" t="s">
-        <v>11</v>
+        <v>166</v>
       </c>
       <c r="B608" s="5" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C608" s="6" t="s">
         <v>689</v>
@@ -16027,46 +16152,46 @@
         <v>1</v>
       </c>
       <c r="E608" s="6"/>
-      <c r="F608" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G608" s="10" t="s">
-        <v>14</v>
-      </c>
+      <c r="F608" s="10"/>
+      <c r="G608" s="10"/>
     </row>
     <row r="609" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A609" s="5" t="s">
-        <v>166</v>
+        <v>11</v>
       </c>
       <c r="B609" s="5" t="s">
-        <v>571</v>
+        <v>547</v>
       </c>
       <c r="C609" s="6" t="s">
         <v>689</v>
       </c>
       <c r="D609" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E609" s="6"/>
-      <c r="F609" s="10"/>
-      <c r="G609" s="10"/>
+        <v>2</v>
+      </c>
+      <c r="E609" s="6">
+        <v>46062</v>
+      </c>
+      <c r="F609" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G609" s="10" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="610" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A610" s="5" t="s">
-        <v>11</v>
+        <v>166</v>
       </c>
       <c r="B610" s="5" t="s">
-        <v>547</v>
+        <v>572</v>
       </c>
       <c r="C610" s="6" t="s">
         <v>689</v>
       </c>
       <c r="D610" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E610" s="6">
-        <v>46062</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E610" s="6"/>
       <c r="F610" s="10" t="s">
         <v>13</v>
       </c>
@@ -16076,13 +16201,13 @@
     </row>
     <row r="611" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A611" s="5" t="s">
-        <v>166</v>
+        <v>11</v>
       </c>
       <c r="B611" s="5" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C611" s="6" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D611" s="5" t="s">
         <v>1</v>
@@ -16100,7 +16225,7 @@
         <v>11</v>
       </c>
       <c r="B612" s="5" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C612" s="6" t="s">
         <v>690</v>
@@ -16121,17 +16246,19 @@
         <v>11</v>
       </c>
       <c r="B613" s="5" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C613" s="6" t="s">
         <v>690</v>
       </c>
       <c r="D613" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E613" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="E613" s="6">
+        <v>46157</v>
+      </c>
       <c r="F613" s="10" t="s">
-        <v>13</v>
+        <v>328</v>
       </c>
       <c r="G613" s="10" t="s">
         <v>14</v>
@@ -16142,19 +16269,17 @@
         <v>11</v>
       </c>
       <c r="B614" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C614" s="6" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D614" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E614" s="6">
-        <v>46157</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E614" s="6"/>
       <c r="F614" s="10" t="s">
-        <v>328</v>
+        <v>13</v>
       </c>
       <c r="G614" s="10" t="s">
         <v>14</v>
@@ -16186,13 +16311,13 @@
         <v>11</v>
       </c>
       <c r="B616" s="5" t="s">
-        <v>576</v>
+        <v>610</v>
       </c>
       <c r="C616" s="6" t="s">
         <v>691</v>
       </c>
       <c r="D616" s="5" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E616" s="6"/>
       <c r="F616" s="10" t="s">
@@ -16207,17 +16332,17 @@
         <v>11</v>
       </c>
       <c r="B617" s="5" t="s">
-        <v>610</v>
+        <v>366</v>
       </c>
       <c r="C617" s="6" t="s">
         <v>691</v>
       </c>
       <c r="D617" s="5" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E617" s="6"/>
       <c r="F617" s="10" t="s">
-        <v>13</v>
+        <v>219</v>
       </c>
       <c r="G617" s="10" t="s">
         <v>14</v>
@@ -16228,17 +16353,17 @@
         <v>11</v>
       </c>
       <c r="B618" s="5" t="s">
-        <v>366</v>
+        <v>456</v>
       </c>
       <c r="C618" s="6" t="s">
         <v>691</v>
       </c>
       <c r="D618" s="5" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E618" s="6"/>
       <c r="F618" s="10" t="s">
-        <v>219</v>
+        <v>13</v>
       </c>
       <c r="G618" s="10" t="s">
         <v>14</v>
@@ -16249,93 +16374,93 @@
         <v>11</v>
       </c>
       <c r="B619" s="5" t="s">
-        <v>456</v>
+        <v>577</v>
       </c>
       <c r="C619" s="6" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D619" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E619" s="6"/>
-      <c r="F619" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G619" s="10" t="s">
-        <v>14</v>
-      </c>
+      <c r="F619" s="10"/>
+      <c r="G619" s="10"/>
     </row>
     <row r="620" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A620" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B620" s="5" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C620" s="6" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D620" s="5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E620" s="6"/>
-      <c r="F620" s="10"/>
-      <c r="G620" s="10"/>
+      <c r="F620" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="G620" s="10" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="621" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A621" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B621" s="5" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C621" s="6" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D621" s="5" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E621" s="6"/>
-      <c r="F621" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="G621" s="10" t="s">
-        <v>14</v>
-      </c>
+      <c r="F621" s="10"/>
+      <c r="G621" s="10"/>
     </row>
     <row r="622" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A622" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B622" s="5" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C622" s="6" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D622" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E622" s="6"/>
-      <c r="F622" s="10"/>
-      <c r="G622" s="10"/>
+      <c r="F622" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G622" s="10" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="623" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A623" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B623" s="5" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C623" s="6" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D623" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E623" s="6"/>
       <c r="F623" s="10" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="G623" s="10" t="s">
         <v>14</v>
@@ -16346,17 +16471,17 @@
         <v>11</v>
       </c>
       <c r="B624" s="5" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C624" s="6" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D624" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E624" s="6"/>
       <c r="F624" s="10" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="G624" s="10" t="s">
         <v>14</v>
@@ -16367,10 +16492,10 @@
         <v>11</v>
       </c>
       <c r="B625" s="5" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C625" s="6" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D625" s="5" t="s">
         <v>1</v>
@@ -16385,13 +16510,13 @@
     </row>
     <row r="626" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A626" s="5" t="s">
-        <v>11</v>
+        <v>166</v>
       </c>
       <c r="B626" s="5" t="s">
-        <v>583</v>
+        <v>498</v>
       </c>
       <c r="C626" s="6" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D626" s="5" t="s">
         <v>1</v>
@@ -16409,17 +16534,17 @@
         <v>166</v>
       </c>
       <c r="B627" s="5" t="s">
-        <v>498</v>
+        <v>584</v>
       </c>
       <c r="C627" s="6" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D627" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E627" s="6"/>
       <c r="F627" s="10" t="s">
-        <v>13</v>
+        <v>611</v>
       </c>
       <c r="G627" s="10" t="s">
         <v>14</v>
@@ -16427,20 +16552,20 @@
     </row>
     <row r="628" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A628" s="5" t="s">
-        <v>166</v>
+        <v>11</v>
       </c>
       <c r="B628" s="5" t="s">
-        <v>584</v>
+        <v>612</v>
       </c>
       <c r="C628" s="6" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D628" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E628" s="6"/>
       <c r="F628" s="10" t="s">
-        <v>611</v>
+        <v>13</v>
       </c>
       <c r="G628" s="10" t="s">
         <v>14</v>
@@ -16451,10 +16576,10 @@
         <v>11</v>
       </c>
       <c r="B629" s="5" t="s">
-        <v>612</v>
+        <v>589</v>
       </c>
       <c r="C629" s="6" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D629" s="5" t="s">
         <v>1</v>
@@ -16472,13 +16597,13 @@
         <v>11</v>
       </c>
       <c r="B630" s="5" t="s">
-        <v>589</v>
-      </c>
-      <c r="C630" s="6" t="s">
-        <v>702</v>
+        <v>593</v>
+      </c>
+      <c r="C630" s="6">
+        <v>45638</v>
       </c>
       <c r="D630" s="5" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E630" s="6"/>
       <c r="F630" s="10" t="s">
@@ -16493,13 +16618,13 @@
         <v>11</v>
       </c>
       <c r="B631" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C631" s="6">
-        <v>45638</v>
+        <v>45639</v>
       </c>
       <c r="D631" s="5" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E631" s="6"/>
       <c r="F631" s="10" t="s">
@@ -16514,10 +16639,10 @@
         <v>11</v>
       </c>
       <c r="B632" s="5" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C632" s="6">
-        <v>45639</v>
+        <v>45642</v>
       </c>
       <c r="D632" s="5" t="s">
         <v>1</v>
@@ -16532,10 +16657,10 @@
     </row>
     <row r="633" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A633" s="5" t="s">
-        <v>11</v>
+        <v>166</v>
       </c>
       <c r="B633" s="5" t="s">
-        <v>594</v>
+        <v>344</v>
       </c>
       <c r="C633" s="6">
         <v>45642</v>
@@ -16553,16 +16678,16 @@
     </row>
     <row r="634" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A634" s="5" t="s">
-        <v>166</v>
+        <v>11</v>
       </c>
       <c r="B634" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="C634" s="6">
-        <v>45642</v>
+        <v>603</v>
+      </c>
+      <c r="C634" s="6" t="s">
+        <v>703</v>
       </c>
       <c r="D634" s="5" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E634" s="6"/>
       <c r="F634" s="10" t="s">
@@ -16577,13 +16702,13 @@
         <v>11</v>
       </c>
       <c r="B635" s="5" t="s">
-        <v>603</v>
-      </c>
-      <c r="C635" s="6" t="s">
-        <v>703</v>
+        <v>588</v>
+      </c>
+      <c r="C635" s="6">
+        <v>45649</v>
       </c>
       <c r="D635" s="5" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E635" s="6"/>
       <c r="F635" s="10" t="s">
@@ -16598,10 +16723,10 @@
         <v>11</v>
       </c>
       <c r="B636" s="5" t="s">
-        <v>588</v>
-      </c>
-      <c r="C636" s="6">
-        <v>45649</v>
+        <v>601</v>
+      </c>
+      <c r="C636" s="6" t="s">
+        <v>704</v>
       </c>
       <c r="D636" s="5" t="s">
         <v>1</v>
@@ -16619,10 +16744,10 @@
         <v>11</v>
       </c>
       <c r="B637" s="5" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C637" s="6" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D637" s="5" t="s">
         <v>1</v>
@@ -16640,13 +16765,13 @@
         <v>11</v>
       </c>
       <c r="B638" s="5" t="s">
-        <v>599</v>
-      </c>
-      <c r="C638" s="6" t="s">
-        <v>705</v>
+        <v>604</v>
+      </c>
+      <c r="C638" s="6">
+        <v>45701</v>
       </c>
       <c r="D638" s="5" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E638" s="6"/>
       <c r="F638" s="10" t="s">
@@ -16661,15 +16786,17 @@
         <v>11</v>
       </c>
       <c r="B639" s="5" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C639" s="6">
         <v>45701</v>
       </c>
       <c r="D639" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E639" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="E639" s="6">
+        <v>46164</v>
+      </c>
       <c r="F639" s="10" t="s">
         <v>13</v>
       </c>
@@ -16682,17 +16809,15 @@
         <v>11</v>
       </c>
       <c r="B640" s="5" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="C640" s="6">
-        <v>45701</v>
+        <v>45706</v>
       </c>
       <c r="D640" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E640" s="6">
-        <v>46164</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="E640" s="6"/>
       <c r="F640" s="10" t="s">
         <v>13</v>
       </c>
@@ -16705,17 +16830,17 @@
         <v>11</v>
       </c>
       <c r="B641" s="5" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C641" s="6">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="D641" s="5" t="s">
-        <v>435</v>
+        <v>1</v>
       </c>
       <c r="E641" s="6"/>
       <c r="F641" s="10" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="G641" s="10" t="s">
         <v>14</v>
@@ -16726,17 +16851,17 @@
         <v>11</v>
       </c>
       <c r="B642" s="5" t="s">
-        <v>586</v>
-      </c>
-      <c r="C642" s="6">
-        <v>45708</v>
+        <v>597</v>
+      </c>
+      <c r="C642" s="6" t="s">
+        <v>706</v>
       </c>
       <c r="D642" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E642" s="6"/>
       <c r="F642" s="10" t="s">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="G642" s="10" t="s">
         <v>14</v>
@@ -16744,13 +16869,13 @@
     </row>
     <row r="643" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A643" s="5" t="s">
-        <v>11</v>
+        <v>166</v>
       </c>
       <c r="B643" s="5" t="s">
-        <v>597</v>
+        <v>487</v>
       </c>
       <c r="C643" s="6" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D643" s="5" t="s">
         <v>1</v>
@@ -16765,10 +16890,10 @@
     </row>
     <row r="644" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A644" s="5" t="s">
-        <v>166</v>
+        <v>11</v>
       </c>
       <c r="B644" s="5" t="s">
-        <v>487</v>
+        <v>596</v>
       </c>
       <c r="C644" s="6" t="s">
         <v>707</v>
@@ -16789,10 +16914,10 @@
         <v>11</v>
       </c>
       <c r="B645" s="5" t="s">
-        <v>596</v>
-      </c>
-      <c r="C645" s="6" t="s">
-        <v>707</v>
+        <v>591</v>
+      </c>
+      <c r="C645" s="6">
+        <v>45730</v>
       </c>
       <c r="D645" s="5" t="s">
         <v>1</v>
@@ -16807,51 +16932,51 @@
     </row>
     <row r="646" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A646" s="5" t="s">
-        <v>11</v>
+        <v>166</v>
       </c>
       <c r="B646" s="5" t="s">
-        <v>591</v>
+        <v>602</v>
       </c>
       <c r="C646" s="6">
         <v>45730</v>
       </c>
       <c r="D646" s="5" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E646" s="6"/>
-      <c r="F646" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G646" s="10" t="s">
-        <v>14</v>
-      </c>
+      <c r="F646" s="10"/>
+      <c r="G646" s="10"/>
     </row>
     <row r="647" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A647" s="5" t="s">
         <v>166</v>
       </c>
       <c r="B647" s="5" t="s">
-        <v>602</v>
+        <v>397</v>
       </c>
       <c r="C647" s="6">
         <v>45730</v>
       </c>
       <c r="D647" s="5" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E647" s="6"/>
-      <c r="F647" s="10"/>
-      <c r="G647" s="10"/>
+      <c r="F647" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G647" s="10" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="648" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A648" s="5" t="s">
         <v>166</v>
       </c>
       <c r="B648" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="C648" s="6">
-        <v>45730</v>
+        <v>587</v>
+      </c>
+      <c r="C648" s="6" t="s">
+        <v>708</v>
       </c>
       <c r="D648" s="5" t="s">
         <v>1</v>
@@ -16869,10 +16994,10 @@
         <v>166</v>
       </c>
       <c r="B649" s="5" t="s">
-        <v>587</v>
-      </c>
-      <c r="C649" s="6" t="s">
-        <v>708</v>
+        <v>444</v>
+      </c>
+      <c r="C649" s="6">
+        <v>45733</v>
       </c>
       <c r="D649" s="5" t="s">
         <v>1</v>
@@ -16887,13 +17012,13 @@
     </row>
     <row r="650" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A650" s="5" t="s">
-        <v>166</v>
+        <v>11</v>
       </c>
       <c r="B650" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="C650" s="6">
-        <v>45733</v>
+        <v>590</v>
+      </c>
+      <c r="C650" s="6" t="s">
+        <v>709</v>
       </c>
       <c r="D650" s="5" t="s">
         <v>1</v>
@@ -16911,17 +17036,17 @@
         <v>11</v>
       </c>
       <c r="B651" s="5" t="s">
-        <v>590</v>
-      </c>
-      <c r="C651" s="6" t="s">
-        <v>709</v>
+        <v>595</v>
+      </c>
+      <c r="C651" s="6">
+        <v>45734</v>
       </c>
       <c r="D651" s="5" t="s">
-        <v>1</v>
+        <v>435</v>
       </c>
       <c r="E651" s="6"/>
       <c r="F651" s="10" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="G651" s="10" t="s">
         <v>14</v>
@@ -16929,20 +17054,20 @@
     </row>
     <row r="652" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A652" s="5" t="s">
-        <v>11</v>
+        <v>166</v>
       </c>
       <c r="B652" s="5" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="C652" s="6">
-        <v>45734</v>
+        <v>45736</v>
       </c>
       <c r="D652" s="5" t="s">
-        <v>435</v>
+        <v>1</v>
       </c>
       <c r="E652" s="6"/>
       <c r="F652" s="10" t="s">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="G652" s="10" t="s">
         <v>14</v>
@@ -16950,13 +17075,13 @@
     </row>
     <row r="653" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A653" s="5" t="s">
-        <v>166</v>
+        <v>11</v>
       </c>
       <c r="B653" s="5" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="C653" s="6">
-        <v>45736</v>
+        <v>45740</v>
       </c>
       <c r="D653" s="5" t="s">
         <v>1</v>
@@ -16974,38 +17099,38 @@
         <v>11</v>
       </c>
       <c r="B654" s="5" t="s">
-        <v>605</v>
-      </c>
-      <c r="C654" s="6">
-        <v>45740</v>
+        <v>637</v>
+      </c>
+      <c r="C654" s="6" t="s">
+        <v>710</v>
       </c>
       <c r="D654" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E654" s="6"/>
       <c r="F654" s="10" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="G654" s="10" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="655" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A655" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B655" s="5" t="s">
-        <v>637</v>
-      </c>
-      <c r="C655" s="6" t="s">
-        <v>710</v>
-      </c>
-      <c r="D655" s="5" t="s">
+      <c r="A655" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B655" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="C655" s="11">
+        <v>45750</v>
+      </c>
+      <c r="D655" s="10" t="s">
         <v>1</v>
       </c>
       <c r="E655" s="6"/>
       <c r="F655" s="10" t="s">
-        <v>71</v>
+        <v>611</v>
       </c>
       <c r="G655" s="10" t="s">
         <v>14</v>
@@ -17013,20 +17138,20 @@
     </row>
     <row r="656" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A656" s="10" t="s">
-        <v>166</v>
+        <v>11</v>
       </c>
       <c r="B656" s="10" t="s">
-        <v>638</v>
-      </c>
-      <c r="C656" s="11">
-        <v>45750</v>
+        <v>617</v>
+      </c>
+      <c r="C656" s="11" t="s">
+        <v>711</v>
       </c>
       <c r="D656" s="10" t="s">
         <v>1</v>
       </c>
       <c r="E656" s="6"/>
       <c r="F656" s="10" t="s">
-        <v>611</v>
+        <v>13</v>
       </c>
       <c r="G656" s="10" t="s">
         <v>14</v>
@@ -17037,7 +17162,7 @@
         <v>11</v>
       </c>
       <c r="B657" s="10" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C657" s="11" t="s">
         <v>711</v>
@@ -17058,10 +17183,10 @@
         <v>11</v>
       </c>
       <c r="B658" s="10" t="s">
-        <v>615</v>
-      </c>
-      <c r="C658" s="11" t="s">
-        <v>711</v>
+        <v>616</v>
+      </c>
+      <c r="C658" s="11">
+        <v>45852</v>
       </c>
       <c r="D658" s="10" t="s">
         <v>1</v>
@@ -17079,7 +17204,7 @@
         <v>11</v>
       </c>
       <c r="B659" s="10" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C659" s="11">
         <v>45852</v>
@@ -17100,10 +17225,10 @@
         <v>11</v>
       </c>
       <c r="B660" s="10" t="s">
-        <v>614</v>
-      </c>
-      <c r="C660" s="11">
-        <v>45852</v>
+        <v>618</v>
+      </c>
+      <c r="C660" s="11" t="s">
+        <v>712</v>
       </c>
       <c r="D660" s="10" t="s">
         <v>1</v>
@@ -17121,10 +17246,10 @@
         <v>11</v>
       </c>
       <c r="B661" s="10" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C661" s="11" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D661" s="10" t="s">
         <v>1</v>
@@ -17142,13 +17267,13 @@
         <v>11</v>
       </c>
       <c r="B662" s="10" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="C662" s="11">
         <v>45868</v>
       </c>
       <c r="D662" s="10" t="s">
-        <v>1</v>
+        <v>435</v>
       </c>
       <c r="E662" s="6"/>
       <c r="F662" s="10" t="s">
@@ -17163,13 +17288,13 @@
         <v>11</v>
       </c>
       <c r="B663" s="10" t="s">
-        <v>619</v>
-      </c>
-      <c r="C663" s="11" t="s">
-        <v>713</v>
+        <v>625</v>
+      </c>
+      <c r="C663" s="11">
+        <v>45868</v>
       </c>
       <c r="D663" s="10" t="s">
-        <v>1</v>
+        <v>435</v>
       </c>
       <c r="E663" s="6"/>
       <c r="F663" s="10" t="s">
@@ -17184,13 +17309,13 @@
         <v>11</v>
       </c>
       <c r="B664" s="10" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="C664" s="11">
-        <v>45868</v>
+        <v>45869</v>
       </c>
       <c r="D664" s="10" t="s">
-        <v>435</v>
+        <v>1</v>
       </c>
       <c r="E664" s="6"/>
       <c r="F664" s="10" t="s">
@@ -17205,18 +17330,16 @@
         <v>11</v>
       </c>
       <c r="B665" s="10" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C665" s="11">
-        <v>45868</v>
+        <v>45869</v>
       </c>
       <c r="D665" s="10" t="s">
         <v>435</v>
       </c>
       <c r="E665" s="6"/>
-      <c r="F665" s="10" t="s">
-        <v>13</v>
-      </c>
+      <c r="F665" s="10"/>
       <c r="G665" s="10" t="s">
         <v>14</v>
       </c>
@@ -17226,18 +17349,16 @@
         <v>11</v>
       </c>
       <c r="B666" s="10" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="C666" s="11">
         <v>45869</v>
       </c>
       <c r="D666" s="10" t="s">
-        <v>1</v>
+        <v>435</v>
       </c>
       <c r="E666" s="6"/>
-      <c r="F666" s="10" t="s">
-        <v>13</v>
-      </c>
+      <c r="F666" s="10"/>
       <c r="G666" s="10" t="s">
         <v>14</v>
       </c>
@@ -17247,16 +17368,18 @@
         <v>11</v>
       </c>
       <c r="B667" s="10" t="s">
-        <v>627</v>
-      </c>
-      <c r="C667" s="11">
-        <v>45869</v>
+        <v>621</v>
+      </c>
+      <c r="C667" s="11" t="s">
+        <v>714</v>
       </c>
       <c r="D667" s="10" t="s">
-        <v>435</v>
+        <v>1</v>
       </c>
       <c r="E667" s="6"/>
-      <c r="F667" s="10"/>
+      <c r="F667" s="10" t="s">
+        <v>13</v>
+      </c>
       <c r="G667" s="10" t="s">
         <v>14</v>
       </c>
@@ -17266,16 +17389,18 @@
         <v>11</v>
       </c>
       <c r="B668" s="10" t="s">
-        <v>628</v>
-      </c>
-      <c r="C668" s="11">
-        <v>45869</v>
+        <v>623</v>
+      </c>
+      <c r="C668" s="11" t="s">
+        <v>715</v>
       </c>
       <c r="D668" s="10" t="s">
-        <v>435</v>
+        <v>1</v>
       </c>
       <c r="E668" s="6"/>
-      <c r="F668" s="10"/>
+      <c r="F668" s="10" t="s">
+        <v>71</v>
+      </c>
       <c r="G668" s="10" t="s">
         <v>14</v>
       </c>
@@ -17285,18 +17410,16 @@
         <v>11</v>
       </c>
       <c r="B669" s="10" t="s">
-        <v>621</v>
-      </c>
-      <c r="C669" s="11" t="s">
-        <v>714</v>
+        <v>622</v>
+      </c>
+      <c r="C669" s="11">
+        <v>45883</v>
       </c>
       <c r="D669" s="10" t="s">
         <v>1</v>
       </c>
       <c r="E669" s="6"/>
-      <c r="F669" s="10" t="s">
-        <v>13</v>
-      </c>
+      <c r="F669" s="10"/>
       <c r="G669" s="10" t="s">
         <v>14</v>
       </c>
@@ -17306,10 +17429,10 @@
         <v>11</v>
       </c>
       <c r="B670" s="10" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="C670" s="11" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D670" s="10" t="s">
         <v>1</v>
@@ -17327,16 +17450,18 @@
         <v>11</v>
       </c>
       <c r="B671" s="10" t="s">
-        <v>622</v>
-      </c>
-      <c r="C671" s="11">
-        <v>45883</v>
+        <v>632</v>
+      </c>
+      <c r="C671" s="11" t="s">
+        <v>716</v>
       </c>
       <c r="D671" s="10" t="s">
         <v>1</v>
       </c>
       <c r="E671" s="6"/>
-      <c r="F671" s="10"/>
+      <c r="F671" s="10" t="s">
+        <v>13</v>
+      </c>
       <c r="G671" s="10" t="s">
         <v>14</v>
       </c>
@@ -17346,17 +17471,17 @@
         <v>11</v>
       </c>
       <c r="B672" s="10" t="s">
-        <v>631</v>
-      </c>
-      <c r="C672" s="11" t="s">
-        <v>716</v>
+        <v>624</v>
+      </c>
+      <c r="C672" s="11">
+        <v>45909</v>
       </c>
       <c r="D672" s="10" t="s">
         <v>1</v>
       </c>
       <c r="E672" s="6"/>
       <c r="F672" s="10" t="s">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="G672" s="10" t="s">
         <v>14</v>
@@ -17367,16 +17492,16 @@
         <v>11</v>
       </c>
       <c r="B673" s="10" t="s">
-        <v>632</v>
-      </c>
-      <c r="C673" s="11" t="s">
-        <v>716</v>
+        <v>629</v>
+      </c>
+      <c r="C673" s="11">
+        <v>45909</v>
       </c>
       <c r="D673" s="10" t="s">
-        <v>1</v>
+        <v>435</v>
       </c>
       <c r="E673" s="6"/>
-      <c r="F673" s="10" t="s">
+      <c r="F673" s="14" t="s">
         <v>13</v>
       </c>
       <c r="G673" s="10" t="s">
@@ -17388,37 +17513,36 @@
         <v>11</v>
       </c>
       <c r="B674" s="10" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="C674" s="11">
         <v>45909</v>
       </c>
       <c r="D674" s="10" t="s">
-        <v>1</v>
+        <v>435</v>
       </c>
       <c r="E674" s="6"/>
       <c r="F674" s="10" t="s">
-        <v>13</v>
+        <v>198</v>
       </c>
       <c r="G674" s="10" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="675" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A675" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B675" s="10" t="s">
-        <v>629</v>
-      </c>
-      <c r="C675" s="11">
-        <v>45909</v>
-      </c>
-      <c r="D675" s="10" t="s">
+      <c r="A675" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B675" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="C675" s="6">
+        <v>45911</v>
+      </c>
+      <c r="D675" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="E675" s="6"/>
-      <c r="F675" s="14" t="s">
+      <c r="F675" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G675" s="10" t="s">
@@ -17426,95 +17550,88 @@
       </c>
     </row>
     <row r="676" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A676" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B676" s="10" t="s">
-        <v>630</v>
-      </c>
-      <c r="C676" s="11">
-        <v>45909</v>
-      </c>
-      <c r="D676" s="10" t="s">
-        <v>435</v>
+      <c r="A676" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B676" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="C676" s="6">
+        <v>45911</v>
+      </c>
+      <c r="D676" s="5" t="s">
+        <v>1</v>
       </c>
       <c r="E676" s="6"/>
       <c r="F676" s="10" t="s">
-        <v>198</v>
+        <v>13</v>
       </c>
       <c r="G676" s="10" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="677" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A677" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B677" s="6" t="s">
-        <v>633</v>
-      </c>
-      <c r="C677" s="6">
-        <v>45911</v>
+      <c r="A677" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B677" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="C677" s="6" t="s">
+        <v>717</v>
       </c>
       <c r="D677" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E677" s="6"/>
+      <c r="F677" s="5"/>
+      <c r="G677" s="5"/>
+    </row>
+    <row r="678" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A678" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B678" s="10" t="s">
+        <v>720</v>
+      </c>
+      <c r="C678" s="11" t="s">
+        <v>730</v>
+      </c>
+      <c r="D678" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E678" s="6"/>
+      <c r="F678" s="10"/>
+      <c r="G678" s="10"/>
+    </row>
+    <row r="679" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A679" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B679" s="10" t="s">
+        <v>734</v>
+      </c>
+      <c r="C679" s="11">
+        <v>46007</v>
+      </c>
+      <c r="D679" s="10" t="s">
         <v>435</v>
       </c>
-      <c r="F677" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G677" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="678" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A678" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B678" s="5" t="s">
-        <v>593</v>
-      </c>
-      <c r="C678" s="6">
-        <v>45911</v>
-      </c>
-      <c r="D678" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E678" s="6"/>
-      <c r="F678" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G678" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="679" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A679" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B679" s="5" t="s">
-        <v>530</v>
-      </c>
-      <c r="C679" s="6" t="s">
-        <v>717</v>
-      </c>
-      <c r="D679" s="5" t="s">
-        <v>1</v>
-      </c>
       <c r="E679" s="6"/>
-      <c r="F679" s="5"/>
-      <c r="G679" s="5"/>
+      <c r="F679" s="10"/>
+      <c r="G679" s="10"/>
     </row>
     <row r="680" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A680" s="10" t="s">
-        <v>166</v>
+        <v>11</v>
       </c>
       <c r="B680" s="10" t="s">
-        <v>472</v>
+        <v>723</v>
       </c>
       <c r="C680" s="11" t="s">
-        <v>728</v>
-      </c>
-      <c r="D680" s="5" t="s">
+        <v>731</v>
+      </c>
+      <c r="D680" s="10" t="s">
         <v>1</v>
       </c>
       <c r="E680" s="6"/>
@@ -17527,37 +17644,33 @@
     </row>
     <row r="681" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A681" s="10" t="s">
-        <v>166</v>
+        <v>11</v>
       </c>
       <c r="B681" s="10" t="s">
-        <v>718</v>
-      </c>
-      <c r="C681" s="11" t="s">
-        <v>729</v>
-      </c>
-      <c r="D681" s="5" t="s">
-        <v>1</v>
+        <v>735</v>
+      </c>
+      <c r="C681" s="11">
+        <v>46007</v>
+      </c>
+      <c r="D681" s="10" t="s">
+        <v>435</v>
       </c>
       <c r="E681" s="6"/>
-      <c r="F681" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G681" s="10" t="s">
-        <v>14</v>
-      </c>
+      <c r="F681" s="10"/>
+      <c r="G681" s="10"/>
     </row>
     <row r="682" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A682" s="10" t="s">
-        <v>166</v>
+        <v>11</v>
       </c>
       <c r="B682" s="10" t="s">
-        <v>719</v>
-      </c>
-      <c r="C682" s="11" t="s">
-        <v>729</v>
-      </c>
-      <c r="D682" s="5" t="s">
-        <v>1</v>
+        <v>736</v>
+      </c>
+      <c r="C682" s="11">
+        <v>46007</v>
+      </c>
+      <c r="D682" s="10" t="s">
+        <v>435</v>
       </c>
       <c r="E682" s="6"/>
       <c r="F682" s="10"/>
@@ -17568,12 +17681,12 @@
         <v>11</v>
       </c>
       <c r="B683" s="10" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C683" s="11" t="s">
-        <v>730</v>
-      </c>
-      <c r="D683" s="5" t="s">
+        <v>731</v>
+      </c>
+      <c r="D683" s="10" t="s">
         <v>1</v>
       </c>
       <c r="E683" s="6"/>
@@ -17590,7 +17703,7 @@
       <c r="C684" s="11" t="s">
         <v>731</v>
       </c>
-      <c r="D684" s="5" t="s">
+      <c r="D684" s="10" t="s">
         <v>1</v>
       </c>
       <c r="E684" s="6"/>
@@ -17606,13 +17719,13 @@
         <v>11</v>
       </c>
       <c r="B685" s="10" t="s">
-        <v>722</v>
-      </c>
-      <c r="C685" s="11" t="s">
-        <v>731</v>
-      </c>
-      <c r="D685" s="5" t="s">
-        <v>1</v>
+        <v>737</v>
+      </c>
+      <c r="C685" s="11">
+        <v>46008</v>
+      </c>
+      <c r="D685" s="10" t="s">
+        <v>435</v>
       </c>
       <c r="E685" s="6"/>
       <c r="F685" s="10"/>
@@ -17623,21 +17736,17 @@
         <v>11</v>
       </c>
       <c r="B686" s="10" t="s">
-        <v>723</v>
-      </c>
-      <c r="C686" s="11" t="s">
-        <v>731</v>
-      </c>
-      <c r="D686" s="5" t="s">
-        <v>1</v>
+        <v>738</v>
+      </c>
+      <c r="C686" s="11">
+        <v>46008</v>
+      </c>
+      <c r="D686" s="10" t="s">
+        <v>435</v>
       </c>
       <c r="E686" s="6"/>
-      <c r="F686" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G686" s="10" t="s">
-        <v>14</v>
-      </c>
+      <c r="F686" s="10"/>
+      <c r="G686" s="10"/>
     </row>
     <row r="687" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A687" s="10" t="s">
@@ -17649,7 +17758,7 @@
       <c r="C687" s="11" t="s">
         <v>732</v>
       </c>
-      <c r="D687" s="5" t="s">
+      <c r="D687" s="10" t="s">
         <v>1</v>
       </c>
       <c r="E687" s="6"/>
@@ -17665,13 +17774,13 @@
         <v>11</v>
       </c>
       <c r="B688" s="10" t="s">
-        <v>725</v>
-      </c>
-      <c r="C688" s="11" t="s">
-        <v>732</v>
-      </c>
-      <c r="D688" s="5" t="s">
-        <v>1</v>
+        <v>739</v>
+      </c>
+      <c r="C688" s="11">
+        <v>46009</v>
+      </c>
+      <c r="D688" s="10" t="s">
+        <v>435</v>
       </c>
       <c r="E688" s="6"/>
       <c r="F688" s="10"/>
@@ -17682,13 +17791,13 @@
         <v>11</v>
       </c>
       <c r="B689" s="10" t="s">
-        <v>726</v>
-      </c>
-      <c r="C689" s="11" t="s">
-        <v>733</v>
-      </c>
-      <c r="D689" s="5" t="s">
-        <v>1</v>
+        <v>740</v>
+      </c>
+      <c r="C689" s="11">
+        <v>46009</v>
+      </c>
+      <c r="D689" s="10" t="s">
+        <v>435</v>
       </c>
       <c r="E689" s="6"/>
       <c r="F689" s="10"/>
@@ -17699,345 +17808,641 @@
         <v>11</v>
       </c>
       <c r="B690" s="10" t="s">
+        <v>741</v>
+      </c>
+      <c r="C690" s="11">
+        <v>46009</v>
+      </c>
+      <c r="D690" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="E690" s="6"/>
+      <c r="F690" s="10"/>
+      <c r="G690" s="10"/>
+    </row>
+    <row r="691" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A691" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B691" s="10" t="s">
+        <v>742</v>
+      </c>
+      <c r="C691" s="11">
+        <v>46009</v>
+      </c>
+      <c r="D691" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="E691" s="6"/>
+      <c r="F691" s="10"/>
+      <c r="G691" s="10"/>
+    </row>
+    <row r="692" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A692" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B692" s="10" t="s">
+        <v>725</v>
+      </c>
+      <c r="C692" s="11" t="s">
+        <v>732</v>
+      </c>
+      <c r="D692" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E692" s="6"/>
+      <c r="F692" s="10"/>
+      <c r="G692" s="10"/>
+    </row>
+    <row r="693" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A693" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B693" s="10" t="s">
+        <v>743</v>
+      </c>
+      <c r="C693" s="11">
+        <v>46009</v>
+      </c>
+      <c r="D693" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="E693" s="6"/>
+      <c r="F693" s="10"/>
+      <c r="G693" s="10"/>
+    </row>
+    <row r="694" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A694" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B694" s="10" t="s">
+        <v>744</v>
+      </c>
+      <c r="C694" s="11">
+        <v>46009</v>
+      </c>
+      <c r="D694" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="E694" s="6"/>
+      <c r="F694" s="10"/>
+      <c r="G694" s="10"/>
+    </row>
+    <row r="695" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A695" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B695" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="C695" s="11" t="s">
+        <v>728</v>
+      </c>
+      <c r="D695" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E695" s="6"/>
+      <c r="F695" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G695" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="696" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A696" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B696" s="10" t="s">
+        <v>726</v>
+      </c>
+      <c r="C696" s="11" t="s">
+        <v>733</v>
+      </c>
+      <c r="D696" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E696" s="6"/>
+      <c r="F696" s="10"/>
+      <c r="G696" s="10"/>
+    </row>
+    <row r="697" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A697" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B697" s="10" t="s">
+        <v>745</v>
+      </c>
+      <c r="C697" s="11">
+        <v>46065</v>
+      </c>
+      <c r="D697" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="E697" s="6"/>
+      <c r="F697" s="10"/>
+      <c r="G697" s="10"/>
+    </row>
+    <row r="698" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A698" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B698" s="10" t="s">
         <v>727</v>
       </c>
-      <c r="C690" s="11" t="s">
+      <c r="C698" s="11" t="s">
         <v>733</v>
       </c>
-      <c r="D690" s="5" t="s">
+      <c r="D698" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E690" s="6"/>
-      <c r="F690" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G690" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="691" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A691" s="5"/>
-      <c r="B691" s="5"/>
-      <c r="C691" s="6"/>
-      <c r="D691" s="5"/>
-      <c r="E691" s="6"/>
-      <c r="F691" s="5"/>
-      <c r="G691" s="5"/>
-    </row>
-    <row r="692" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A692" s="5"/>
-      <c r="B692" s="5"/>
-      <c r="C692" s="6"/>
-      <c r="D692" s="5"/>
-      <c r="E692" s="6"/>
-      <c r="F692" s="5"/>
-      <c r="G692" s="5"/>
-    </row>
-    <row r="693" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A693" s="5"/>
-      <c r="B693" s="5"/>
-      <c r="C693" s="6"/>
-      <c r="D693" s="5"/>
-      <c r="E693" s="6"/>
-      <c r="F693" s="5"/>
-      <c r="G693" s="5"/>
-    </row>
-    <row r="694" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A694" s="5"/>
-      <c r="B694" s="5"/>
-      <c r="C694" s="6"/>
-      <c r="D694" s="5"/>
-      <c r="E694" s="6"/>
-      <c r="F694" s="5"/>
-      <c r="G694" s="5"/>
-    </row>
-    <row r="695" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A695" s="5"/>
-      <c r="B695" s="5"/>
-      <c r="C695" s="6"/>
-      <c r="D695" s="5"/>
-      <c r="E695" s="6"/>
-      <c r="F695" s="5"/>
-      <c r="G695" s="5"/>
-    </row>
-    <row r="696" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A696" s="5"/>
-      <c r="B696" s="5"/>
-      <c r="C696" s="6"/>
-      <c r="D696" s="5"/>
-      <c r="E696" s="6"/>
-      <c r="F696" s="5"/>
-      <c r="G696" s="5"/>
-    </row>
-    <row r="697" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A697" s="5"/>
-      <c r="B697" s="5"/>
-      <c r="C697" s="6"/>
-      <c r="D697" s="5"/>
-      <c r="E697" s="6"/>
-      <c r="F697" s="5"/>
-      <c r="G697" s="5"/>
-    </row>
-    <row r="698" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A698" s="5"/>
-      <c r="B698" s="5"/>
-      <c r="C698" s="6"/>
-      <c r="D698" s="5"/>
       <c r="E698" s="6"/>
-      <c r="F698" s="5"/>
-      <c r="G698" s="5"/>
+      <c r="F698" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G698" s="10" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="699" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A699" s="5"/>
-      <c r="B699" s="5"/>
-      <c r="C699" s="6"/>
-      <c r="D699" s="5"/>
+      <c r="A699" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B699" s="10" t="s">
+        <v>718</v>
+      </c>
+      <c r="C699" s="11" t="s">
+        <v>729</v>
+      </c>
+      <c r="D699" s="10" t="s">
+        <v>1</v>
+      </c>
       <c r="E699" s="6"/>
-      <c r="F699" s="5"/>
-      <c r="G699" s="5"/>
+      <c r="F699" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G699" s="10" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="700" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A700" s="5"/>
-      <c r="B700" s="5"/>
-      <c r="C700" s="6"/>
-      <c r="D700" s="5"/>
+      <c r="A700" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B700" s="10" t="s">
+        <v>746</v>
+      </c>
+      <c r="C700" s="11">
+        <v>46066</v>
+      </c>
+      <c r="D700" s="10" t="s">
+        <v>1</v>
+      </c>
       <c r="E700" s="6"/>
-      <c r="F700" s="5"/>
-      <c r="G700" s="5"/>
+      <c r="F700" s="10"/>
+      <c r="G700" s="10"/>
     </row>
     <row r="701" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A701" s="5"/>
-      <c r="B701" s="5"/>
-      <c r="C701" s="6"/>
-      <c r="D701" s="5"/>
+      <c r="A701" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B701" s="10" t="s">
+        <v>747</v>
+      </c>
+      <c r="C701" s="11">
+        <v>46066</v>
+      </c>
+      <c r="D701" s="10" t="s">
+        <v>435</v>
+      </c>
       <c r="E701" s="6"/>
-      <c r="F701" s="5"/>
-      <c r="G701" s="5"/>
+      <c r="F701" s="10"/>
+      <c r="G701" s="10"/>
     </row>
     <row r="702" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A702" s="5"/>
-      <c r="B702" s="5"/>
-      <c r="C702" s="6"/>
-      <c r="D702" s="5"/>
+      <c r="A702" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B702" s="10" t="s">
+        <v>719</v>
+      </c>
+      <c r="C702" s="11" t="s">
+        <v>729</v>
+      </c>
+      <c r="D702" s="10" t="s">
+        <v>1</v>
+      </c>
       <c r="E702" s="6"/>
-      <c r="F702" s="5"/>
-      <c r="G702" s="5"/>
+      <c r="F702" s="10"/>
+      <c r="G702" s="10"/>
     </row>
     <row r="703" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A703" s="5"/>
-      <c r="B703" s="5"/>
-      <c r="C703" s="6"/>
-      <c r="D703" s="5"/>
+      <c r="A703" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B703" s="10" t="s">
+        <v>748</v>
+      </c>
+      <c r="C703" s="11">
+        <v>46072</v>
+      </c>
+      <c r="D703" s="10" t="s">
+        <v>435</v>
+      </c>
       <c r="E703" s="6"/>
-      <c r="F703" s="5"/>
-      <c r="G703" s="5"/>
+      <c r="F703" s="10"/>
+      <c r="G703" s="10"/>
     </row>
     <row r="704" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A704" s="5"/>
-      <c r="B704" s="5"/>
-      <c r="C704" s="6"/>
-      <c r="D704" s="5"/>
+      <c r="A704" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B704" s="10" t="s">
+        <v>629</v>
+      </c>
+      <c r="C704" s="11">
+        <v>46072</v>
+      </c>
+      <c r="D704" s="10" t="s">
+        <v>435</v>
+      </c>
       <c r="E704" s="6"/>
-      <c r="F704" s="5"/>
-      <c r="G704" s="5"/>
+      <c r="F704" s="10"/>
+      <c r="G704" s="10"/>
     </row>
     <row r="705" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A705" s="5"/>
-      <c r="B705" s="5"/>
-      <c r="C705" s="6"/>
-      <c r="D705" s="5"/>
+      <c r="A705" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B705" s="10" t="s">
+        <v>749</v>
+      </c>
+      <c r="C705" s="11">
+        <v>46076</v>
+      </c>
+      <c r="D705" s="10" t="s">
+        <v>1</v>
+      </c>
       <c r="E705" s="6"/>
-      <c r="F705" s="5"/>
-      <c r="G705" s="5"/>
+      <c r="F705" s="10"/>
+      <c r="G705" s="10"/>
     </row>
     <row r="706" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A706" s="5"/>
-      <c r="B706" s="5"/>
-      <c r="C706" s="6"/>
-      <c r="D706" s="5"/>
+      <c r="A706" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B706" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="C706" s="11">
+        <v>46076</v>
+      </c>
+      <c r="D706" s="10" t="s">
+        <v>1</v>
+      </c>
       <c r="E706" s="6"/>
-      <c r="F706" s="5"/>
-      <c r="G706" s="5"/>
+      <c r="F706" s="10"/>
+      <c r="G706" s="10"/>
     </row>
     <row r="707" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A707" s="5"/>
-      <c r="B707" s="5"/>
-      <c r="C707" s="6"/>
-      <c r="D707" s="5"/>
+      <c r="A707" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B707" s="10" t="s">
+        <v>750</v>
+      </c>
+      <c r="C707" s="11">
+        <v>46077</v>
+      </c>
+      <c r="D707" s="10" t="s">
+        <v>1</v>
+      </c>
       <c r="E707" s="6"/>
-      <c r="F707" s="5"/>
-      <c r="G707" s="5"/>
+      <c r="F707" s="10"/>
+      <c r="G707" s="10"/>
     </row>
     <row r="708" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A708" s="5"/>
-      <c r="B708" s="5"/>
-      <c r="C708" s="6"/>
-      <c r="D708" s="5"/>
+      <c r="A708" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B708" s="10" t="s">
+        <v>751</v>
+      </c>
+      <c r="C708" s="11">
+        <v>46078</v>
+      </c>
+      <c r="D708" s="10" t="s">
+        <v>435</v>
+      </c>
       <c r="E708" s="6"/>
-      <c r="F708" s="5"/>
-      <c r="G708" s="5"/>
+      <c r="F708" s="10"/>
+      <c r="G708" s="10"/>
     </row>
     <row r="709" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A709" s="5"/>
-      <c r="B709" s="5"/>
-      <c r="C709" s="6"/>
-      <c r="D709" s="5"/>
+      <c r="A709" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B709" s="10" t="s">
+        <v>752</v>
+      </c>
+      <c r="C709" s="11">
+        <v>46078</v>
+      </c>
+      <c r="D709" s="10" t="s">
+        <v>1</v>
+      </c>
       <c r="E709" s="6"/>
-      <c r="F709" s="5"/>
-      <c r="G709" s="5"/>
+      <c r="F709" s="10"/>
+      <c r="G709" s="10"/>
     </row>
     <row r="710" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A710" s="5"/>
-      <c r="B710" s="5"/>
-      <c r="C710" s="6"/>
-      <c r="D710" s="5"/>
+      <c r="A710" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B710" s="10" t="s">
+        <v>753</v>
+      </c>
+      <c r="C710" s="11">
+        <v>46081</v>
+      </c>
+      <c r="D710" s="10" t="s">
+        <v>1</v>
+      </c>
       <c r="E710" s="6"/>
-      <c r="F710" s="5"/>
-      <c r="G710" s="5"/>
+      <c r="F710" s="10"/>
+      <c r="G710" s="10"/>
     </row>
     <row r="711" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A711" s="5"/>
-      <c r="B711" s="5"/>
-      <c r="C711" s="6"/>
-      <c r="D711" s="5"/>
+      <c r="A711" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B711" s="10" t="s">
+        <v>754</v>
+      </c>
+      <c r="C711" s="11">
+        <v>46087</v>
+      </c>
+      <c r="D711" s="10" t="s">
+        <v>435</v>
+      </c>
       <c r="E711" s="6"/>
-      <c r="F711" s="5"/>
-      <c r="G711" s="5"/>
+      <c r="F711" s="10"/>
+      <c r="G711" s="10"/>
     </row>
     <row r="712" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A712" s="5"/>
-      <c r="B712" s="5"/>
-      <c r="C712" s="6"/>
-      <c r="D712" s="5"/>
+      <c r="A712" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B712" s="10" t="s">
+        <v>755</v>
+      </c>
+      <c r="C712" s="11">
+        <v>46087</v>
+      </c>
+      <c r="D712" s="10" t="s">
+        <v>1</v>
+      </c>
       <c r="E712" s="6"/>
-      <c r="F712" s="5"/>
-      <c r="G712" s="5"/>
+      <c r="F712" s="10"/>
+      <c r="G712" s="10"/>
     </row>
     <row r="713" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A713" s="5"/>
-      <c r="B713" s="5"/>
-      <c r="C713" s="6"/>
-      <c r="D713" s="5"/>
+      <c r="A713" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B713" s="10" t="s">
+        <v>756</v>
+      </c>
+      <c r="C713" s="11">
+        <v>46087</v>
+      </c>
+      <c r="D713" s="10" t="s">
+        <v>435</v>
+      </c>
       <c r="E713" s="6"/>
-      <c r="F713" s="5"/>
-      <c r="G713" s="5"/>
+      <c r="F713" s="10"/>
+      <c r="G713" s="10"/>
     </row>
     <row r="714" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A714" s="5"/>
-      <c r="B714" s="5"/>
-      <c r="C714" s="6"/>
-      <c r="D714" s="5"/>
+      <c r="A714" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B714" s="10" t="s">
+        <v>757</v>
+      </c>
+      <c r="C714" s="11">
+        <v>46087</v>
+      </c>
+      <c r="D714" s="10" t="s">
+        <v>1</v>
+      </c>
       <c r="E714" s="6"/>
-      <c r="F714" s="5"/>
-      <c r="G714" s="5"/>
+      <c r="F714" s="10"/>
+      <c r="G714" s="10"/>
     </row>
     <row r="715" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A715" s="5"/>
-      <c r="B715" s="5"/>
-      <c r="C715" s="6"/>
-      <c r="D715" s="5"/>
+      <c r="A715" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B715" s="10" t="s">
+        <v>758</v>
+      </c>
+      <c r="C715" s="11">
+        <v>46087</v>
+      </c>
+      <c r="D715" s="10" t="s">
+        <v>435</v>
+      </c>
       <c r="E715" s="6"/>
-      <c r="F715" s="5"/>
-      <c r="G715" s="5"/>
+      <c r="F715" s="10"/>
+      <c r="G715" s="10"/>
     </row>
     <row r="716" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A716" s="5"/>
-      <c r="B716" s="5"/>
-      <c r="C716" s="6"/>
-      <c r="D716" s="5"/>
+      <c r="A716" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B716" s="10" t="s">
+        <v>759</v>
+      </c>
+      <c r="C716" s="11">
+        <v>46087</v>
+      </c>
+      <c r="D716" s="10" t="s">
+        <v>435</v>
+      </c>
       <c r="E716" s="6"/>
-      <c r="F716" s="5"/>
-      <c r="G716" s="5"/>
+      <c r="F716" s="10"/>
+      <c r="G716" s="10"/>
     </row>
     <row r="717" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A717" s="5"/>
-      <c r="B717" s="5"/>
-      <c r="C717" s="6"/>
-      <c r="D717" s="5"/>
+      <c r="A717" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B717" s="10" t="s">
+        <v>760</v>
+      </c>
+      <c r="C717" s="11">
+        <v>46087</v>
+      </c>
+      <c r="D717" s="10" t="s">
+        <v>1</v>
+      </c>
       <c r="E717" s="6"/>
-      <c r="F717" s="5"/>
-      <c r="G717" s="5"/>
+      <c r="F717" s="10"/>
+      <c r="G717" s="10"/>
     </row>
     <row r="718" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A718" s="5"/>
-      <c r="B718" s="5"/>
-      <c r="C718" s="6"/>
-      <c r="D718" s="5"/>
+      <c r="A718" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B718" s="10" t="s">
+        <v>761</v>
+      </c>
+      <c r="C718" s="11">
+        <v>46101</v>
+      </c>
+      <c r="D718" s="10" t="s">
+        <v>1</v>
+      </c>
       <c r="E718" s="6"/>
-      <c r="F718" s="5"/>
-      <c r="G718" s="5"/>
+      <c r="F718" s="10"/>
+      <c r="G718" s="10"/>
     </row>
     <row r="719" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A719" s="5"/>
-      <c r="B719" s="5"/>
-      <c r="C719" s="6"/>
-      <c r="D719" s="5"/>
+      <c r="A719" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B719" s="10" t="s">
+        <v>762</v>
+      </c>
+      <c r="C719" s="11">
+        <v>46101</v>
+      </c>
+      <c r="D719" s="10" t="s">
+        <v>1</v>
+      </c>
       <c r="E719" s="6"/>
-      <c r="F719" s="5"/>
-      <c r="G719" s="5"/>
+      <c r="F719" s="10"/>
+      <c r="G719" s="10"/>
     </row>
     <row r="720" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A720" s="5"/>
-      <c r="B720" s="5"/>
-      <c r="C720" s="6"/>
-      <c r="D720" s="5"/>
+      <c r="A720" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B720" s="10" t="s">
+        <v>763</v>
+      </c>
+      <c r="C720" s="11">
+        <v>46119</v>
+      </c>
+      <c r="D720" s="10" t="s">
+        <v>1</v>
+      </c>
       <c r="E720" s="6"/>
-      <c r="F720" s="5"/>
-      <c r="G720" s="5"/>
+      <c r="F720" s="10"/>
+      <c r="G720" s="10"/>
     </row>
     <row r="721" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A721" s="5"/>
-      <c r="B721" s="5"/>
-      <c r="C721" s="6"/>
-      <c r="D721" s="5"/>
+      <c r="A721" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B721" s="10" t="s">
+        <v>764</v>
+      </c>
+      <c r="C721" s="11">
+        <v>46119</v>
+      </c>
+      <c r="D721" s="10" t="s">
+        <v>435</v>
+      </c>
       <c r="E721" s="6"/>
-      <c r="F721" s="5"/>
-      <c r="G721" s="5"/>
+      <c r="F721" s="10"/>
+      <c r="G721" s="10"/>
     </row>
     <row r="722" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A722" s="5"/>
-      <c r="B722" s="5"/>
-      <c r="C722" s="6"/>
-      <c r="D722" s="5"/>
+      <c r="A722" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B722" s="10" t="s">
+        <v>765</v>
+      </c>
+      <c r="C722" s="11">
+        <v>46119</v>
+      </c>
+      <c r="D722" s="10" t="s">
+        <v>435</v>
+      </c>
       <c r="E722" s="6"/>
-      <c r="F722" s="5"/>
-      <c r="G722" s="5"/>
+      <c r="F722" s="10"/>
+      <c r="G722" s="10"/>
     </row>
     <row r="723" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A723" s="5"/>
-      <c r="B723" s="5"/>
-      <c r="C723" s="6"/>
-      <c r="D723" s="5"/>
+      <c r="A723" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B723" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C723" s="11">
+        <v>46119</v>
+      </c>
+      <c r="D723" s="10" t="s">
+        <v>1</v>
+      </c>
       <c r="E723" s="6"/>
-      <c r="F723" s="5"/>
-      <c r="G723" s="5"/>
+      <c r="F723" s="10"/>
+      <c r="G723" s="10"/>
     </row>
     <row r="724" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A724" s="5"/>
-      <c r="B724" s="5"/>
-      <c r="C724" s="6"/>
-      <c r="D724" s="5"/>
+      <c r="A724" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B724" s="10" t="s">
+        <v>767</v>
+      </c>
+      <c r="C724" s="11">
+        <v>46120</v>
+      </c>
+      <c r="D724" s="10" t="s">
+        <v>435</v>
+      </c>
       <c r="E724" s="6"/>
-      <c r="F724" s="5"/>
-      <c r="G724" s="5"/>
+      <c r="F724" s="10"/>
+      <c r="G724" s="10"/>
     </row>
     <row r="725" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A725" s="5"/>
-      <c r="B725" s="5"/>
-      <c r="C725" s="6"/>
-      <c r="D725" s="5"/>
+      <c r="A725" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B725" s="10" t="s">
+        <v>768</v>
+      </c>
+      <c r="C725" s="11">
+        <v>46120</v>
+      </c>
+      <c r="D725" s="10" t="s">
+        <v>1</v>
+      </c>
       <c r="E725" s="6"/>
-      <c r="F725" s="5"/>
-      <c r="G725" s="5"/>
+      <c r="F725" s="10"/>
+      <c r="G725" s="10"/>
     </row>
     <row r="726" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A726" s="5"/>
-      <c r="B726" s="5"/>
-      <c r="C726" s="6"/>
-      <c r="D726" s="5"/>
+      <c r="A726" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B726" s="10" t="s">
+        <v>558</v>
+      </c>
+      <c r="C726" s="11">
+        <v>46125</v>
+      </c>
+      <c r="D726" s="10" t="s">
+        <v>1</v>
+      </c>
       <c r="E726" s="6"/>
-      <c r="F726" s="5"/>
-      <c r="G726" s="5"/>
+      <c r="F726" s="10"/>
+      <c r="G726" s="10"/>
     </row>
     <row r="727" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A727" s="5"/>
@@ -19146,24 +19551,8 @@
       <c r="F849" s="5"/>
       <c r="G849" s="5"/>
     </row>
-    <row r="850" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A850" s="5"/>
-      <c r="B850" s="5"/>
-      <c r="C850" s="6"/>
-      <c r="D850" s="5"/>
-      <c r="E850" s="6"/>
-      <c r="F850" s="5"/>
-      <c r="G850" s="5"/>
-    </row>
-    <row r="851" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A851" s="5"/>
-      <c r="B851" s="5"/>
-      <c r="C851" s="6"/>
-      <c r="D851" s="5"/>
-      <c r="E851" s="6"/>
-      <c r="F851" s="5"/>
-      <c r="G851" s="5"/>
-    </row>
+    <row r="850" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="852" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="853" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="854" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -19230,21 +19619,22 @@
     <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <autoFilter ref="A1:G655" xr:uid="{00000000-0001-0000-0800-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G622">
-      <sortCondition ref="C2:C622"/>
-      <sortCondition ref="B2:B622"/>
+  <autoFilter ref="A1:G654" xr:uid="{00000000-0001-0000-0800-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G621">
+      <sortCondition ref="C2:C621"/>
+      <sortCondition ref="B2:B621"/>
     </sortState>
   </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G557">
     <sortCondition ref="C2:C557"/>
     <sortCondition ref="B2:B557"/>
   </sortState>
-  <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="3" stopIfTrue="1"/>
+  <conditionalFormatting sqref="B1:B677 B727:B1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="4" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B678:B726">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
